--- a/Assets/Excel/Equipment.xlsx
+++ b/Assets/Excel/Equipment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E46030-ABB6-4DE9-856F-90326021F168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8227441A-A2E6-4730-BE25-6EBE3FDAB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6210" yWindow="2055" windowWidth="21645" windowHeight="13440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10380" yWindow="1125" windowWidth="21645" windowHeight="13440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentLevel" sheetId="1" r:id="rId1"/>
@@ -76,15 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Atk</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
     <t>Agility</t>
   </si>
   <si>
@@ -105,6 +96,18 @@
   </si>
   <si>
     <t>装备等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,19 +469,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -500,19 +503,19 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1239,16 +1242,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1272,17 +1275,17 @@
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1403,16 +1406,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1436,17 +1439,17 @@
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">

--- a/Assets/Excel/Equipment.xlsx
+++ b/Assets/Excel/Equipment.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8227441A-A2E6-4730-BE25-6EBE3FDAB3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5241BFE5-3832-49C6-AADD-022C9E09D7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10380" yWindow="1125" windowWidth="21645" windowHeight="13440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentLevel" sheetId="1" r:id="rId1"/>
-    <sheet name="AttrRatio" sheetId="2" r:id="rId2"/>
-    <sheet name="SlotRatio" sheetId="3" r:id="rId3"/>
-    <sheet name="EuipmentDesc(道具信息后面再补）" sheetId="4" r:id="rId4"/>
+    <sheet name="EuipmentDesc(道具信息后面再补）" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,19 +50,7 @@
     <t>ItemName</t>
   </si>
   <si>
-    <t>ID索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rarity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -166,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -177,7 +163,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -469,19 +454,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -489,33 +474,33 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1233,436 +1218,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65171F79-22EB-4BA0-8471-F3B29D69B934}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1.2</v>
-      </c>
-      <c r="C5">
-        <v>1.2</v>
-      </c>
-      <c r="D5">
-        <v>1.2</v>
-      </c>
-      <c r="E5">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>1.4</v>
-      </c>
-      <c r="C6">
-        <v>1.4</v>
-      </c>
-      <c r="D6">
-        <v>1.4</v>
-      </c>
-      <c r="E6">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>1.6</v>
-      </c>
-      <c r="C7">
-        <v>1.6</v>
-      </c>
-      <c r="D7">
-        <v>1.6</v>
-      </c>
-      <c r="E7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>1.8</v>
-      </c>
-      <c r="C8">
-        <v>1.8</v>
-      </c>
-      <c r="D8">
-        <v>1.8</v>
-      </c>
-      <c r="E8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4C4091-3047-45A6-ABEB-A1EC7A7045ED}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>0.8</v>
-      </c>
-      <c r="C5">
-        <v>0.8</v>
-      </c>
-      <c r="D5">
-        <v>0.8</v>
-      </c>
-      <c r="E5">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>0.75</v>
-      </c>
-      <c r="C6">
-        <v>0.75</v>
-      </c>
-      <c r="D6">
-        <v>0.75</v>
-      </c>
-      <c r="E6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>0.9</v>
-      </c>
-      <c r="C7">
-        <v>0.9</v>
-      </c>
-      <c r="D7">
-        <v>0.9</v>
-      </c>
-      <c r="E7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>0.8</v>
-      </c>
-      <c r="C8">
-        <v>0.8</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
-      <c r="E8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>0.75</v>
-      </c>
-      <c r="C9">
-        <v>0.75</v>
-      </c>
-      <c r="D9">
-        <v>0.75</v>
-      </c>
-      <c r="E9">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>0.9</v>
-      </c>
-      <c r="C10">
-        <v>0.9</v>
-      </c>
-      <c r="D10">
-        <v>0.9</v>
-      </c>
-      <c r="E10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>0.8</v>
-      </c>
-      <c r="C11">
-        <v>0.8</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
-      <c r="E11">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>0.75</v>
-      </c>
-      <c r="C12">
-        <v>0.75</v>
-      </c>
-      <c r="D12">
-        <v>0.75</v>
-      </c>
-      <c r="E12">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>0.8</v>
-      </c>
-      <c r="C13">
-        <v>0.8</v>
-      </c>
-      <c r="D13">
-        <v>0.8</v>
-      </c>
-      <c r="E13">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>0.75</v>
-      </c>
-      <c r="C14">
-        <v>0.75</v>
-      </c>
-      <c r="D14">
-        <v>0.75</v>
-      </c>
-      <c r="E14">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>12</v>
-      </c>
-      <c r="B15">
-        <v>0.9</v>
-      </c>
-      <c r="C15">
-        <v>0.9</v>
-      </c>
-      <c r="D15">
-        <v>0.9</v>
-      </c>
-      <c r="E15">
-        <v>0.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97390096-4EB2-4541-B6EE-AD8398430746}">
   <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1676,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="4:5" x14ac:dyDescent="0.2">
@@ -1692,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="4:5" x14ac:dyDescent="0.2">

--- a/Assets/Excel/Equipment.xlsx
+++ b/Assets/Excel/Equipment.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5241BFE5-3832-49C6-AADD-022C9E09D7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D722B7-8906-425D-BA2B-2D38135FA594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="1515" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentLevel" sheetId="1" r:id="rId1"/>
-    <sheet name="EuipmentDesc(道具信息后面再补）" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,30 +34,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>道具名称</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-  </si>
-  <si>
     <t>Float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具图标</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -443,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -454,19 +436,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -474,33 +456,33 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -712,19 +694,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <f t="shared" ref="B16:B39" si="0">B4+40</f>
+        <f t="shared" ref="B16:B79" si="0">B4+40</f>
         <v>140</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:C39" si="1">C4+15</f>
+        <f t="shared" ref="C16:C79" si="1">C4+15</f>
         <v>35</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" ref="D16:D39" si="2">D15+350</f>
+        <f t="shared" ref="D16:D79" si="2">D15+350</f>
         <v>1350</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" ref="E16:E39" si="3">E15+5</f>
+        <f t="shared" ref="E16:E79" si="3">E15+5</f>
         <v>15</v>
       </c>
     </row>
@@ -1211,192 +1193,1349 @@
         <v>130</v>
       </c>
     </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97390096-4EB2-4541-B6EE-AD8398430746}">
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C40" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="2"/>
+        <v>9750</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C41" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D41" s="2">
+        <f t="shared" si="2"/>
+        <v>10100</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C42" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D42" s="2">
+        <f t="shared" si="2"/>
+        <v>10450</v>
+      </c>
+      <c r="E42" s="2">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="2"/>
+        <v>10800</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="2"/>
+        <v>11150</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="3"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D45" s="2">
+        <f t="shared" si="2"/>
+        <v>11500</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D46" s="2">
+        <f t="shared" si="2"/>
+        <v>11850</v>
+      </c>
+      <c r="E46" s="2">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>44</v>
+      </c>
+      <c r="B47" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C47" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="2"/>
+        <v>12200</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" si="3"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D48" s="2">
+        <f t="shared" si="2"/>
+        <v>12550</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>46</v>
+      </c>
+      <c r="B49" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C49" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D49" s="2">
+        <f t="shared" si="2"/>
+        <v>12900</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D50" s="2">
+        <f t="shared" si="2"/>
+        <v>13250</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="C51" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="D51" s="2">
+        <f t="shared" si="2"/>
+        <v>13600</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>49</v>
+      </c>
+      <c r="B52" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="2"/>
+        <v>13950</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="3"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C53" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="2"/>
+        <v>14300</v>
+      </c>
+      <c r="E53" s="2">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>51</v>
+      </c>
+      <c r="B54" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C54" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="2"/>
+        <v>14650</v>
+      </c>
+      <c r="E54" s="2">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>52</v>
+      </c>
+      <c r="B55" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C55" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D55" s="2">
+        <f t="shared" si="2"/>
+        <v>15000</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>53</v>
+      </c>
+      <c r="B56" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C56" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="2"/>
+        <v>15350</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>54</v>
+      </c>
+      <c r="B57" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" si="2"/>
+        <v>15700</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>55</v>
+      </c>
+      <c r="B58" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="2"/>
+        <v>16050</v>
+      </c>
+      <c r="E58" s="2">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>56</v>
+      </c>
+      <c r="B59" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C59" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" si="2"/>
+        <v>16400</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>57</v>
+      </c>
+      <c r="B60" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C60" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="2"/>
+        <v>16750</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>58</v>
+      </c>
+      <c r="B61" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C61" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="2"/>
+        <v>17100</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>59</v>
+      </c>
+      <c r="B62" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C62" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="2"/>
+        <v>17450</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>60</v>
+      </c>
+      <c r="B63" s="2">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="C63" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="2"/>
+        <v>17800</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>61</v>
+      </c>
+      <c r="B64" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C64" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="2"/>
+        <v>18150</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>62</v>
+      </c>
+      <c r="B65" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C65" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="2"/>
+        <v>18500</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="3"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>63</v>
+      </c>
+      <c r="B66" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C66" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D66" s="2">
+        <f t="shared" si="2"/>
+        <v>18850</v>
+      </c>
+      <c r="E66" s="2">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>64</v>
+      </c>
+      <c r="B67" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C67" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D67" s="2">
+        <f t="shared" si="2"/>
+        <v>19200</v>
+      </c>
+      <c r="E67" s="2">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>65</v>
+      </c>
+      <c r="B68" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C68" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D68" s="2">
+        <f t="shared" si="2"/>
+        <v>19550</v>
+      </c>
+      <c r="E68" s="2">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>66</v>
+      </c>
+      <c r="B69" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D69" s="2">
+        <f t="shared" si="2"/>
+        <v>19900</v>
+      </c>
+      <c r="E69" s="2">
+        <f t="shared" si="3"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>67</v>
+      </c>
+      <c r="B70" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C70" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D70" s="2">
+        <f t="shared" si="2"/>
+        <v>20250</v>
+      </c>
+      <c r="E70" s="2">
+        <f t="shared" si="3"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>68</v>
+      </c>
+      <c r="B71" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D71" s="2">
+        <f t="shared" si="2"/>
+        <v>20600</v>
+      </c>
+      <c r="E71" s="2">
+        <f t="shared" si="3"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>69</v>
+      </c>
+      <c r="B72" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C72" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D72" s="2">
+        <f t="shared" si="2"/>
+        <v>20950</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>70</v>
+      </c>
+      <c r="B73" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C73" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D73" s="2">
+        <f t="shared" si="2"/>
+        <v>21300</v>
+      </c>
+      <c r="E73" s="2">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C74" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D74" s="2">
+        <f t="shared" si="2"/>
+        <v>21650</v>
+      </c>
+      <c r="E74" s="2">
+        <f t="shared" si="3"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>72</v>
+      </c>
+      <c r="B75" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="C75" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="D75" s="2">
+        <f t="shared" si="2"/>
+        <v>22000</v>
+      </c>
+      <c r="E75" s="2">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>73</v>
+      </c>
+      <c r="B76" s="2">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="C76" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D76" s="2">
+        <f t="shared" si="2"/>
+        <v>22350</v>
+      </c>
+      <c r="E76" s="2">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>74</v>
+      </c>
+      <c r="B77" s="2">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="C77" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D77" s="2">
+        <f t="shared" si="2"/>
+        <v>22700</v>
+      </c>
+      <c r="E77" s="2">
+        <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>75</v>
+      </c>
+      <c r="B78" s="2">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="C78" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D78" s="2">
+        <f t="shared" si="2"/>
+        <v>23050</v>
+      </c>
+      <c r="E78" s="2">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>76</v>
+      </c>
+      <c r="B79" s="2">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="C79" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D79" s="2">
+        <f t="shared" si="2"/>
+        <v>23400</v>
+      </c>
+      <c r="E79" s="2">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>77</v>
+      </c>
+      <c r="B80" s="2">
+        <f t="shared" ref="B80:B105" si="4">B68+40</f>
+        <v>340</v>
+      </c>
+      <c r="C80" s="2">
+        <f t="shared" ref="C80:C105" si="5">C68+15</f>
+        <v>110</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:D105" si="6">D79+350</f>
+        <v>23750</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" ref="E80:E105" si="7">E79+5</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>78</v>
+      </c>
+      <c r="B81" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C81" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D81" s="2">
+        <f t="shared" si="6"/>
+        <v>24100</v>
+      </c>
+      <c r="E81" s="2">
+        <f t="shared" si="7"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>79</v>
+      </c>
+      <c r="B82" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C82" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" si="6"/>
+        <v>24450</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="7"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>80</v>
+      </c>
+      <c r="B83" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C83" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" si="6"/>
+        <v>24800</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="7"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>81</v>
+      </c>
+      <c r="B84" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C84" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" si="6"/>
+        <v>25150</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>82</v>
+      </c>
+      <c r="B85" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C85" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="6"/>
+        <v>25500</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="7"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>83</v>
+      </c>
+      <c r="B86" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C86" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="6"/>
+        <v>25850</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>84</v>
+      </c>
+      <c r="B87" s="2">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="C87" s="2">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="6"/>
+        <v>26200</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="7"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>85</v>
+      </c>
+      <c r="B88" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C88" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="6"/>
+        <v>26550</v>
+      </c>
+      <c r="E88" s="2">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>86</v>
+      </c>
+      <c r="B89" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C89" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D89" s="2">
+        <f t="shared" si="6"/>
+        <v>26900</v>
+      </c>
+      <c r="E89" s="2">
+        <f t="shared" si="7"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>87</v>
+      </c>
+      <c r="B90" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C90" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D90" s="2">
+        <f t="shared" si="6"/>
+        <v>27250</v>
+      </c>
+      <c r="E90" s="2">
+        <f t="shared" si="7"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>88</v>
+      </c>
+      <c r="B91" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C91" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D91" s="2">
+        <f t="shared" si="6"/>
+        <v>27600</v>
+      </c>
+      <c r="E91" s="2">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>89</v>
+      </c>
+      <c r="B92" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C92" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D92" s="2">
+        <f t="shared" si="6"/>
+        <v>27950</v>
+      </c>
+      <c r="E92" s="2">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>90</v>
+      </c>
+      <c r="B93" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C93" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D93" s="2">
+        <f t="shared" si="6"/>
+        <v>28300</v>
+      </c>
+      <c r="E93" s="2">
+        <f t="shared" si="7"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>91</v>
+      </c>
+      <c r="B94" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C94" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D94" s="2">
+        <f t="shared" si="6"/>
+        <v>28650</v>
+      </c>
+      <c r="E94" s="2">
+        <f t="shared" si="7"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>92</v>
+      </c>
+      <c r="B95" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C95" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D95" s="2">
+        <f t="shared" si="6"/>
+        <v>29000</v>
+      </c>
+      <c r="E95" s="2">
+        <f t="shared" si="7"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>93</v>
+      </c>
+      <c r="B96" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C96" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D96" s="2">
+        <f t="shared" si="6"/>
+        <v>29350</v>
+      </c>
+      <c r="E96" s="2">
+        <f t="shared" si="7"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>94</v>
+      </c>
+      <c r="B97" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C97" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D97" s="2">
+        <f t="shared" si="6"/>
+        <v>29700</v>
+      </c>
+      <c r="E97" s="2">
+        <f t="shared" si="7"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>95</v>
+      </c>
+      <c r="B98" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C98" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D98" s="2">
+        <f t="shared" si="6"/>
+        <v>30050</v>
+      </c>
+      <c r="E98" s="2">
+        <f t="shared" si="7"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>96</v>
+      </c>
+      <c r="B99" s="2">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="C99" s="2">
+        <f t="shared" si="5"/>
+        <v>125</v>
+      </c>
+      <c r="D99" s="2">
+        <f t="shared" si="6"/>
+        <v>30400</v>
+      </c>
+      <c r="E99" s="2">
+        <f t="shared" si="7"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>97</v>
+      </c>
+      <c r="B100" s="2">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="C100" s="2">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="D100" s="2">
+        <f t="shared" si="6"/>
+        <v>30750</v>
+      </c>
+      <c r="E100" s="2">
+        <f t="shared" si="7"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>98</v>
+      </c>
+      <c r="B101" s="2">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="C101" s="2">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="D101" s="2">
+        <f t="shared" si="6"/>
+        <v>31100</v>
+      </c>
+      <c r="E101" s="2">
+        <f t="shared" si="7"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>99</v>
+      </c>
+      <c r="B102" s="2">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="C102" s="2">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="D102" s="2">
+        <f t="shared" si="6"/>
+        <v>31450</v>
+      </c>
+      <c r="E102" s="2">
+        <f t="shared" si="7"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>100</v>
+      </c>
+      <c r="B103" s="2">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="C103" s="2">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="D103" s="2">
+        <f t="shared" si="6"/>
+        <v>31800</v>
+      </c>
+      <c r="E103" s="2">
+        <f t="shared" si="7"/>
+        <v>450</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Excel/Equipment.xlsx
+++ b/Assets/Excel/Equipment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D722B7-8906-425D-BA2B-2D38135FA594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972460B1-F68D-46E6-92BF-063880F0EA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="1515" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29055" yWindow="945" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentLevel" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +78,54 @@
     <t>Hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CounterRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DodgeRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StunRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LifeStealRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -108,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,6 +166,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -134,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -143,6 +203,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -425,16 +491,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
     <col min="2" max="4" width="7.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -450,8 +528,50 @@
       <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1" t="str">
+        <f>"抗"&amp;F1</f>
+        <v>抗暴击</v>
+      </c>
+      <c r="M1" s="1" t="str">
+        <f>"抗"&amp;G1</f>
+        <v>抗反击</v>
+      </c>
+      <c r="N1" s="1" t="str">
+        <f>"抗"&amp;H1</f>
+        <v>抗连击</v>
+      </c>
+      <c r="O1" s="1" t="str">
+        <f>"抗"&amp;I1</f>
+        <v>抗闪避</v>
+      </c>
+      <c r="P1" s="1" t="str">
+        <f>"抗"&amp;J1</f>
+        <v>抗击晕</v>
+      </c>
+      <c r="Q1" s="1" t="str">
+        <f>"抗"&amp;K1</f>
+        <v>抗吸血</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -467,8 +587,44 @@
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -484,8 +640,50 @@
       <c r="E3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <f>"Anti"&amp;F3</f>
+        <v>AntiCritRate</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <f>"Anti"&amp;G3</f>
+        <v>AntiCounterRate</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <f>"Anti"&amp;H3</f>
+        <v>AntiComboRate</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <f>"Anti"&amp;I3</f>
+        <v>AntiDodgeRate</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <f>"Anti"&amp;J3</f>
+        <v>AntiStunRate</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <f>"Anti"&amp;K3</f>
+        <v>AntiLifeStealRate</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -501,8 +699,44 @@
       <c r="E4" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -518,8 +752,44 @@
       <c r="E5" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -535,8 +805,44 @@
       <c r="E6" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -552,8 +858,44 @@
       <c r="E7" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -569,8 +911,44 @@
       <c r="E8" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -586,8 +964,44 @@
       <c r="E9" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -603,8 +1017,44 @@
       <c r="E10" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -620,8 +1070,44 @@
       <c r="E11" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -637,8 +1123,44 @@
       <c r="E12" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -654,8 +1176,44 @@
       <c r="E13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" s="2">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -671,8 +1229,44 @@
       <c r="E14" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="J14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -688,8 +1282,44 @@
       <c r="E15" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15" s="2">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2">
+        <v>6</v>
+      </c>
+      <c r="H15" s="2">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2">
+        <v>6</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -709,8 +1339,44 @@
         <f t="shared" ref="E16:E79" si="3">E15+5</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="G16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="H16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="K16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -730,8 +1396,44 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" s="2">
+        <v>7</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7</v>
+      </c>
+      <c r="H17" s="2">
+        <v>7</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7</v>
+      </c>
+      <c r="J17" s="2">
+        <v>7</v>
+      </c>
+      <c r="K17" s="2">
+        <v>7</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -751,8 +1453,44 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="K18" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="L18" s="2">
+        <v>3</v>
+      </c>
+      <c r="M18" s="2">
+        <v>3</v>
+      </c>
+      <c r="N18" s="2">
+        <v>3</v>
+      </c>
+      <c r="O18" s="2">
+        <v>3</v>
+      </c>
+      <c r="P18" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -772,8 +1510,44 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="M19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="N19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="O19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="P19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -793,8 +1567,44 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="H20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="J20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="K20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="L20" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M20" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="N20" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="O20" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="P20" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -814,8 +1624,44 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" s="2">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>9</v>
+      </c>
+      <c r="H21" s="2">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9</v>
+      </c>
+      <c r="J21" s="2">
+        <v>9</v>
+      </c>
+      <c r="K21" s="2">
+        <v>9</v>
+      </c>
+      <c r="L21" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="M21" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="N21" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="O21" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="P21" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -835,8 +1681,44 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="G22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="H22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="K22" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="L22" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="M22" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O22" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P22" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -856,8 +1738,44 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10</v>
+      </c>
+      <c r="K23" s="2">
+        <v>10</v>
+      </c>
+      <c r="L23" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="N23" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P23" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -877,8 +1795,44 @@
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="G24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="I24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="K24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="L24" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="M24" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O24" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P24" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -898,8 +1852,44 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="2">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2">
+        <v>11</v>
+      </c>
+      <c r="H25" s="2">
+        <v>11</v>
+      </c>
+      <c r="I25" s="2">
+        <v>11</v>
+      </c>
+      <c r="J25" s="2">
+        <v>11</v>
+      </c>
+      <c r="K25" s="2">
+        <v>11</v>
+      </c>
+      <c r="L25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="N25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -919,8 +1909,44 @@
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="H26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="I26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="L26" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="M26" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="N26" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="O26" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P26" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -940,8 +1966,44 @@
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27" s="2">
+        <v>12</v>
+      </c>
+      <c r="G27" s="2">
+        <v>12</v>
+      </c>
+      <c r="H27" s="2">
+        <v>12</v>
+      </c>
+      <c r="I27" s="2">
+        <v>12</v>
+      </c>
+      <c r="J27" s="2">
+        <v>12</v>
+      </c>
+      <c r="K27" s="2">
+        <v>12</v>
+      </c>
+      <c r="L27" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="M27" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="N27" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="O27" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="P27" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -961,8 +2023,44 @@
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="G28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="J28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="K28" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="L28" s="2">
+        <v>6</v>
+      </c>
+      <c r="M28" s="2">
+        <v>6</v>
+      </c>
+      <c r="N28" s="2">
+        <v>6</v>
+      </c>
+      <c r="O28" s="2">
+        <v>6</v>
+      </c>
+      <c r="P28" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -982,8 +2080,44 @@
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" s="2">
+        <v>13</v>
+      </c>
+      <c r="H29" s="2">
+        <v>13</v>
+      </c>
+      <c r="I29" s="2">
+        <v>13</v>
+      </c>
+      <c r="J29" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" s="2">
+        <v>13</v>
+      </c>
+      <c r="L29" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="M29" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="N29" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="O29" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="P29" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -1003,8 +2137,44 @@
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="I30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="J30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="K30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="L30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="M30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="N30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="O30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="P30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -1024,8 +2194,44 @@
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31" s="2">
+        <v>14</v>
+      </c>
+      <c r="G31" s="2">
+        <v>14</v>
+      </c>
+      <c r="H31" s="2">
+        <v>14</v>
+      </c>
+      <c r="I31" s="2">
+        <v>14</v>
+      </c>
+      <c r="J31" s="2">
+        <v>14</v>
+      </c>
+      <c r="K31" s="2">
+        <v>14</v>
+      </c>
+      <c r="L31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="M31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="O31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="P31" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -1045,8 +2251,44 @@
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="G32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="I32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="J32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="K32" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="L32" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="M32" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="N32" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="O32" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="P32" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -1066,8 +2308,44 @@
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2">
+        <v>15</v>
+      </c>
+      <c r="I33" s="2">
+        <v>15</v>
+      </c>
+      <c r="J33" s="2">
+        <v>15</v>
+      </c>
+      <c r="K33" s="2">
+        <v>15</v>
+      </c>
+      <c r="L33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="M33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="O33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="P33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -1087,8 +2365,44 @@
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="I34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="J34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="K34" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="L34" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="M34" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="N34" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="O34" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="P34" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -1108,8 +2422,44 @@
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35" s="2">
+        <v>16</v>
+      </c>
+      <c r="G35" s="2">
+        <v>16</v>
+      </c>
+      <c r="H35" s="2">
+        <v>16</v>
+      </c>
+      <c r="I35" s="2">
+        <v>16</v>
+      </c>
+      <c r="J35" s="2">
+        <v>16</v>
+      </c>
+      <c r="K35" s="2">
+        <v>16</v>
+      </c>
+      <c r="L35" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="M35" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N35" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="O35" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="P35" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -1129,8 +2479,44 @@
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="I36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="J36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="K36" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="L36" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="M36" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N36" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="O36" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="P36" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -1150,8 +2536,44 @@
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F37" s="2">
+        <v>17</v>
+      </c>
+      <c r="G37" s="2">
+        <v>17</v>
+      </c>
+      <c r="H37" s="2">
+        <v>17</v>
+      </c>
+      <c r="I37" s="2">
+        <v>17</v>
+      </c>
+      <c r="J37" s="2">
+        <v>17</v>
+      </c>
+      <c r="K37" s="2">
+        <v>17</v>
+      </c>
+      <c r="L37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="M37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="P37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -1171,8 +2593,44 @@
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="G38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="I38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="J38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="K38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="L38" s="2">
+        <v>9</v>
+      </c>
+      <c r="M38" s="2">
+        <v>9</v>
+      </c>
+      <c r="N38" s="2">
+        <v>9</v>
+      </c>
+      <c r="O38" s="2">
+        <v>9</v>
+      </c>
+      <c r="P38" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -1192,8 +2650,44 @@
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39" s="2">
+        <v>18</v>
+      </c>
+      <c r="G39" s="2">
+        <v>18</v>
+      </c>
+      <c r="H39" s="2">
+        <v>18</v>
+      </c>
+      <c r="I39" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" s="2">
+        <v>18</v>
+      </c>
+      <c r="K39" s="2">
+        <v>18</v>
+      </c>
+      <c r="L39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="O39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="P39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -1213,8 +2707,44 @@
         <f t="shared" si="3"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="G40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="H40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="I40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="J40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="K40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="L40" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="M40" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="N40" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="O40" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="P40" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -1234,8 +2764,44 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41" s="2">
+        <v>19</v>
+      </c>
+      <c r="G41" s="2">
+        <v>19</v>
+      </c>
+      <c r="H41" s="2">
+        <v>19</v>
+      </c>
+      <c r="I41" s="2">
+        <v>19</v>
+      </c>
+      <c r="J41" s="2">
+        <v>19</v>
+      </c>
+      <c r="K41" s="2">
+        <v>19</v>
+      </c>
+      <c r="L41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="M41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="N41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="O41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="P41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -1255,8 +2821,44 @@
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="G42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="H42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="I42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="J42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="K42" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="L42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -1276,8 +2878,44 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F43" s="2">
+        <v>20</v>
+      </c>
+      <c r="G43" s="2">
+        <v>20</v>
+      </c>
+      <c r="H43" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" s="2">
+        <v>20</v>
+      </c>
+      <c r="J43" s="2">
+        <v>20</v>
+      </c>
+      <c r="K43" s="2">
+        <v>20</v>
+      </c>
+      <c r="L43" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="M43" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="N43" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O43" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="P43" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -1297,8 +2935,44 @@
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="G44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="I44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="J44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="K44" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="L44" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="M44" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="N44" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O44" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="P44" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -1318,8 +2992,44 @@
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" s="2">
+        <v>21</v>
+      </c>
+      <c r="G45" s="2">
+        <v>21</v>
+      </c>
+      <c r="H45" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" s="2">
+        <v>21</v>
+      </c>
+      <c r="K45" s="2">
+        <v>21</v>
+      </c>
+      <c r="L45" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="M45" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="N45" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="O45" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="P45" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -1339,8 +3049,44 @@
         <f t="shared" si="3"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="G46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="H46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="I46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="J46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="K46" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="L46" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="M46" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="N46" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="O46" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="P46" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -1360,8 +3106,44 @@
         <f t="shared" si="3"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" s="2">
+        <v>22</v>
+      </c>
+      <c r="G47" s="2">
+        <v>22</v>
+      </c>
+      <c r="H47" s="2">
+        <v>22</v>
+      </c>
+      <c r="I47" s="2">
+        <v>22</v>
+      </c>
+      <c r="J47" s="2">
+        <v>22</v>
+      </c>
+      <c r="K47" s="2">
+        <v>22</v>
+      </c>
+      <c r="L47" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="M47" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="N47" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="O47" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="P47" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -1381,8 +3163,44 @@
         <f t="shared" si="3"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="G48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="H48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="I48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="J48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="K48" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="L48" s="2">
+        <v>12</v>
+      </c>
+      <c r="M48" s="2">
+        <v>12</v>
+      </c>
+      <c r="N48" s="2">
+        <v>12</v>
+      </c>
+      <c r="O48" s="2">
+        <v>12</v>
+      </c>
+      <c r="P48" s="2">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -1402,8 +3220,44 @@
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F49" s="2">
+        <v>23</v>
+      </c>
+      <c r="G49" s="2">
+        <v>23</v>
+      </c>
+      <c r="H49" s="2">
+        <v>23</v>
+      </c>
+      <c r="I49" s="2">
+        <v>23</v>
+      </c>
+      <c r="J49" s="2">
+        <v>23</v>
+      </c>
+      <c r="K49" s="2">
+        <v>23</v>
+      </c>
+      <c r="L49" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="M49" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="N49" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="O49" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="P49" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -1423,8 +3277,44 @@
         <f t="shared" si="3"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="G50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="H50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="I50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="J50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="K50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="L50" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="M50" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="N50" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="O50" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="P50" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -1444,8 +3334,44 @@
         <f t="shared" si="3"/>
         <v>190</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F51" s="2">
+        <v>24</v>
+      </c>
+      <c r="G51" s="2">
+        <v>24</v>
+      </c>
+      <c r="H51" s="2">
+        <v>24</v>
+      </c>
+      <c r="I51" s="2">
+        <v>24</v>
+      </c>
+      <c r="J51" s="2">
+        <v>24</v>
+      </c>
+      <c r="K51" s="2">
+        <v>24</v>
+      </c>
+      <c r="L51" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="M51" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="N51" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="O51" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="P51" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -1465,8 +3391,44 @@
         <f t="shared" si="3"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="G52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="H52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="I52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="J52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="K52" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="L52" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="M52" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="N52" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="O52" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="P52" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -1486,8 +3448,44 @@
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53" s="2">
+        <v>25</v>
+      </c>
+      <c r="G53" s="2">
+        <v>25</v>
+      </c>
+      <c r="H53" s="2">
+        <v>25</v>
+      </c>
+      <c r="I53" s="2">
+        <v>25</v>
+      </c>
+      <c r="J53" s="2">
+        <v>25</v>
+      </c>
+      <c r="K53" s="2">
+        <v>25</v>
+      </c>
+      <c r="L53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="M53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="N53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="O53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="P53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -1507,8 +3505,44 @@
         <f t="shared" si="3"/>
         <v>205</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="G54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="H54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="I54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="J54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="K54" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="L54" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M54" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="N54" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="O54" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="P54" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -1528,8 +3562,44 @@
         <f t="shared" si="3"/>
         <v>210</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F55" s="2">
+        <v>26</v>
+      </c>
+      <c r="G55" s="2">
+        <v>26</v>
+      </c>
+      <c r="H55" s="2">
+        <v>26</v>
+      </c>
+      <c r="I55" s="2">
+        <v>26</v>
+      </c>
+      <c r="J55" s="2">
+        <v>26</v>
+      </c>
+      <c r="K55" s="2">
+        <v>26</v>
+      </c>
+      <c r="L55" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M55" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="N55" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="O55" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="P55" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -1549,8 +3619,44 @@
         <f t="shared" si="3"/>
         <v>215</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="G56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="H56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="I56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="J56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="K56" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="L56" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="M56" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="N56" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="O56" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="P56" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -1570,8 +3676,44 @@
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F57" s="2">
+        <v>27</v>
+      </c>
+      <c r="G57" s="2">
+        <v>27</v>
+      </c>
+      <c r="H57" s="2">
+        <v>27</v>
+      </c>
+      <c r="I57" s="2">
+        <v>27</v>
+      </c>
+      <c r="J57" s="2">
+        <v>27</v>
+      </c>
+      <c r="K57" s="2">
+        <v>27</v>
+      </c>
+      <c r="L57" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M57" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="N57" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="O57" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="P57" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -1591,8 +3733,44 @@
         <f t="shared" si="3"/>
         <v>225</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="G58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="H58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="I58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="J58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="K58" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="L58" s="2">
+        <v>15</v>
+      </c>
+      <c r="M58" s="2">
+        <v>15</v>
+      </c>
+      <c r="N58" s="2">
+        <v>15</v>
+      </c>
+      <c r="O58" s="2">
+        <v>15</v>
+      </c>
+      <c r="P58" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -1612,8 +3790,44 @@
         <f t="shared" si="3"/>
         <v>230</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59" s="2">
+        <v>28</v>
+      </c>
+      <c r="G59" s="2">
+        <v>28</v>
+      </c>
+      <c r="H59" s="2">
+        <v>28</v>
+      </c>
+      <c r="I59" s="2">
+        <v>28</v>
+      </c>
+      <c r="J59" s="2">
+        <v>28</v>
+      </c>
+      <c r="K59" s="2">
+        <v>28</v>
+      </c>
+      <c r="L59" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="M59" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="N59" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="O59" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="P59" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -1633,8 +3847,44 @@
         <f t="shared" si="3"/>
         <v>235</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="H60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="I60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="J60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="K60" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="L60" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="M60" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="N60" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="O60" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="P60" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -1654,8 +3904,44 @@
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61" s="2">
+        <v>29</v>
+      </c>
+      <c r="G61" s="2">
+        <v>29</v>
+      </c>
+      <c r="H61" s="2">
+        <v>29</v>
+      </c>
+      <c r="I61" s="2">
+        <v>29</v>
+      </c>
+      <c r="J61" s="2">
+        <v>29</v>
+      </c>
+      <c r="K61" s="2">
+        <v>29</v>
+      </c>
+      <c r="L61" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="M61" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="N61" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="O61" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="P61" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -1675,8 +3961,44 @@
         <f t="shared" si="3"/>
         <v>245</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="G62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="H62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="I62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="J62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="K62" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="L62" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="M62" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="N62" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="O62" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="P62" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -1696,8 +4018,44 @@
         <f t="shared" si="3"/>
         <v>250</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63" s="2">
+        <v>30</v>
+      </c>
+      <c r="G63" s="2">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2">
+        <v>30</v>
+      </c>
+      <c r="J63" s="2">
+        <v>30</v>
+      </c>
+      <c r="K63" s="2">
+        <v>30</v>
+      </c>
+      <c r="L63" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="M63" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="N63" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="O63" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="P63" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -1717,8 +4075,44 @@
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="G64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="H64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="I64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="J64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="K64" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="L64" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="M64" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="N64" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="O64" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="P64" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>62</v>
       </c>
@@ -1738,8 +4132,44 @@
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65" s="2">
+        <v>31</v>
+      </c>
+      <c r="G65" s="2">
+        <v>31</v>
+      </c>
+      <c r="H65" s="2">
+        <v>31</v>
+      </c>
+      <c r="I65" s="2">
+        <v>31</v>
+      </c>
+      <c r="J65" s="2">
+        <v>31</v>
+      </c>
+      <c r="K65" s="2">
+        <v>31</v>
+      </c>
+      <c r="L65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="M65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="O65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="P65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -1759,8 +4189,44 @@
         <f t="shared" si="3"/>
         <v>265</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="G66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="H66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="I66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="J66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="K66" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="L66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="M66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="N66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="O66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="P66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>64</v>
       </c>
@@ -1780,8 +4246,44 @@
         <f t="shared" si="3"/>
         <v>270</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67" s="2">
+        <v>32</v>
+      </c>
+      <c r="G67" s="2">
+        <v>32</v>
+      </c>
+      <c r="H67" s="2">
+        <v>32</v>
+      </c>
+      <c r="I67" s="2">
+        <v>32</v>
+      </c>
+      <c r="J67" s="2">
+        <v>32</v>
+      </c>
+      <c r="K67" s="2">
+        <v>32</v>
+      </c>
+      <c r="L67" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="M67" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="N67" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="O67" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="P67" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -1801,8 +4303,44 @@
         <f t="shared" si="3"/>
         <v>275</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="G68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="H68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="I68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="J68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="K68" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="L68" s="2">
+        <v>18</v>
+      </c>
+      <c r="M68" s="2">
+        <v>18</v>
+      </c>
+      <c r="N68" s="2">
+        <v>18</v>
+      </c>
+      <c r="O68" s="2">
+        <v>18</v>
+      </c>
+      <c r="P68" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>66</v>
       </c>
@@ -1822,8 +4360,44 @@
         <f t="shared" si="3"/>
         <v>280</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F69" s="2">
+        <v>33</v>
+      </c>
+      <c r="G69" s="2">
+        <v>33</v>
+      </c>
+      <c r="H69" s="2">
+        <v>33</v>
+      </c>
+      <c r="I69" s="2">
+        <v>33</v>
+      </c>
+      <c r="J69" s="2">
+        <v>33</v>
+      </c>
+      <c r="K69" s="2">
+        <v>33</v>
+      </c>
+      <c r="L69" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="M69" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="N69" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="O69" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="P69" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -1843,8 +4417,44 @@
         <f t="shared" si="3"/>
         <v>285</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="G70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="H70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="I70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="J70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="K70" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="L70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="M70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="N70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="O70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="P70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>68</v>
       </c>
@@ -1864,8 +4474,44 @@
         <f t="shared" si="3"/>
         <v>290</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F71" s="2">
+        <v>34</v>
+      </c>
+      <c r="G71" s="2">
+        <v>34</v>
+      </c>
+      <c r="H71" s="2">
+        <v>34</v>
+      </c>
+      <c r="I71" s="2">
+        <v>34</v>
+      </c>
+      <c r="J71" s="2">
+        <v>34</v>
+      </c>
+      <c r="K71" s="2">
+        <v>34</v>
+      </c>
+      <c r="L71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="N71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="O71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="P71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>69</v>
       </c>
@@ -1885,8 +4531,44 @@
         <f t="shared" si="3"/>
         <v>295</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="G72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="H72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="I72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="J72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="K72" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="L72" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="M72" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="N72" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="O72" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="P72" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>70</v>
       </c>
@@ -1906,8 +4588,44 @@
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F73" s="2">
+        <v>35</v>
+      </c>
+      <c r="G73" s="2">
+        <v>35</v>
+      </c>
+      <c r="H73" s="2">
+        <v>35</v>
+      </c>
+      <c r="I73" s="2">
+        <v>35</v>
+      </c>
+      <c r="J73" s="2">
+        <v>35</v>
+      </c>
+      <c r="K73" s="2">
+        <v>35</v>
+      </c>
+      <c r="L73" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="M73" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="N73" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="O73" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="P73" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>71</v>
       </c>
@@ -1927,8 +4645,44 @@
         <f t="shared" si="3"/>
         <v>305</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="G74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="H74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="I74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="J74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="K74" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="L74" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="M74" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="N74" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="O74" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="P74" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>72</v>
       </c>
@@ -1948,8 +4702,44 @@
         <f t="shared" si="3"/>
         <v>310</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F75" s="2">
+        <v>36</v>
+      </c>
+      <c r="G75" s="2">
+        <v>36</v>
+      </c>
+      <c r="H75" s="2">
+        <v>36</v>
+      </c>
+      <c r="I75" s="2">
+        <v>36</v>
+      </c>
+      <c r="J75" s="2">
+        <v>36</v>
+      </c>
+      <c r="K75" s="2">
+        <v>36</v>
+      </c>
+      <c r="L75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="M75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="N75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="O75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="P75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>73</v>
       </c>
@@ -1969,8 +4759,44 @@
         <f t="shared" si="3"/>
         <v>315</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="G76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="H76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="I76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="J76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="K76" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="L76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="M76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="N76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="O76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="P76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>74</v>
       </c>
@@ -1990,8 +4816,44 @@
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77" s="2">
+        <v>37</v>
+      </c>
+      <c r="G77" s="2">
+        <v>37</v>
+      </c>
+      <c r="H77" s="2">
+        <v>37</v>
+      </c>
+      <c r="I77" s="2">
+        <v>37</v>
+      </c>
+      <c r="J77" s="2">
+        <v>37</v>
+      </c>
+      <c r="K77" s="2">
+        <v>37</v>
+      </c>
+      <c r="L77" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="M77" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="N77" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="O77" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="P77" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>75</v>
       </c>
@@ -2011,8 +4873,44 @@
         <f t="shared" si="3"/>
         <v>325</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="G78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="H78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="I78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="J78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="K78" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="L78" s="2">
+        <v>21</v>
+      </c>
+      <c r="M78" s="2">
+        <v>21</v>
+      </c>
+      <c r="N78" s="2">
+        <v>21</v>
+      </c>
+      <c r="O78" s="2">
+        <v>21</v>
+      </c>
+      <c r="P78" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>76</v>
       </c>
@@ -2032,29 +4930,101 @@
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F79" s="2">
+        <v>38</v>
+      </c>
+      <c r="G79" s="2">
+        <v>38</v>
+      </c>
+      <c r="H79" s="2">
+        <v>38</v>
+      </c>
+      <c r="I79" s="2">
+        <v>38</v>
+      </c>
+      <c r="J79" s="2">
+        <v>38</v>
+      </c>
+      <c r="K79" s="2">
+        <v>38</v>
+      </c>
+      <c r="L79" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="M79" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="N79" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="O79" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="P79" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>77</v>
       </c>
       <c r="B80" s="2">
-        <f t="shared" ref="B80:B105" si="4">B68+40</f>
+        <f t="shared" ref="B80:B103" si="4">B68+40</f>
         <v>340</v>
       </c>
       <c r="C80" s="2">
-        <f t="shared" ref="C80:C105" si="5">C68+15</f>
+        <f t="shared" ref="C80:C103" si="5">C68+15</f>
         <v>110</v>
       </c>
       <c r="D80" s="2">
-        <f t="shared" ref="D80:D105" si="6">D79+350</f>
+        <f t="shared" ref="D80:D103" si="6">D79+350</f>
         <v>23750</v>
       </c>
       <c r="E80" s="2">
-        <f t="shared" ref="E80:E105" si="7">E79+5</f>
+        <f t="shared" ref="E80:E103" si="7">E79+5</f>
         <v>335</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="G80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="H80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="I80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="J80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="K80" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="L80" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="M80" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="N80" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="O80" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="P80" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>78</v>
       </c>
@@ -2074,8 +5044,44 @@
         <f t="shared" si="7"/>
         <v>340</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F81" s="2">
+        <v>39</v>
+      </c>
+      <c r="G81" s="2">
+        <v>39</v>
+      </c>
+      <c r="H81" s="2">
+        <v>39</v>
+      </c>
+      <c r="I81" s="2">
+        <v>39</v>
+      </c>
+      <c r="J81" s="2">
+        <v>39</v>
+      </c>
+      <c r="K81" s="2">
+        <v>39</v>
+      </c>
+      <c r="L81" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="M81" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="N81" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="O81" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="P81" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>79</v>
       </c>
@@ -2095,8 +5101,44 @@
         <f t="shared" si="7"/>
         <v>345</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="G82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="H82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="I82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="J82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="K82" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="L82" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="M82" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="N82" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="O82" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="P82" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>80</v>
       </c>
@@ -2116,8 +5158,44 @@
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F83" s="2">
+        <v>40</v>
+      </c>
+      <c r="G83" s="2">
+        <v>40</v>
+      </c>
+      <c r="H83" s="2">
+        <v>40</v>
+      </c>
+      <c r="I83" s="2">
+        <v>40</v>
+      </c>
+      <c r="J83" s="2">
+        <v>40</v>
+      </c>
+      <c r="K83" s="2">
+        <v>40</v>
+      </c>
+      <c r="L83" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="M83" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="N83" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="O83" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="P83" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>81</v>
       </c>
@@ -2137,8 +5215,44 @@
         <f t="shared" si="7"/>
         <v>355</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="G84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="H84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="I84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="J84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="K84" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="L84" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="M84" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="N84" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="O84" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="P84" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>82</v>
       </c>
@@ -2158,8 +5272,44 @@
         <f t="shared" si="7"/>
         <v>360</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F85" s="2">
+        <v>41</v>
+      </c>
+      <c r="G85" s="2">
+        <v>41</v>
+      </c>
+      <c r="H85" s="2">
+        <v>41</v>
+      </c>
+      <c r="I85" s="2">
+        <v>41</v>
+      </c>
+      <c r="J85" s="2">
+        <v>41</v>
+      </c>
+      <c r="K85" s="2">
+        <v>41</v>
+      </c>
+      <c r="L85" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="M85" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="N85" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="O85" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="P85" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>83</v>
       </c>
@@ -2179,8 +5329,44 @@
         <f t="shared" si="7"/>
         <v>365</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="G86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="H86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="I86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="J86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="K86" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="L86" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="M86" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="N86" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="O86" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="P86" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>84</v>
       </c>
@@ -2200,8 +5386,44 @@
         <f t="shared" si="7"/>
         <v>370</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F87" s="2">
+        <v>42</v>
+      </c>
+      <c r="G87" s="2">
+        <v>42</v>
+      </c>
+      <c r="H87" s="2">
+        <v>42</v>
+      </c>
+      <c r="I87" s="2">
+        <v>42</v>
+      </c>
+      <c r="J87" s="2">
+        <v>42</v>
+      </c>
+      <c r="K87" s="2">
+        <v>42</v>
+      </c>
+      <c r="L87" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="M87" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="N87" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="O87" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="P87" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>85</v>
       </c>
@@ -2221,8 +5443,44 @@
         <f t="shared" si="7"/>
         <v>375</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="G88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="H88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="I88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="J88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="K88" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="L88" s="2">
+        <v>24</v>
+      </c>
+      <c r="M88" s="2">
+        <v>24</v>
+      </c>
+      <c r="N88" s="2">
+        <v>24</v>
+      </c>
+      <c r="O88" s="2">
+        <v>24</v>
+      </c>
+      <c r="P88" s="2">
+        <v>24</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>86</v>
       </c>
@@ -2242,8 +5500,44 @@
         <f t="shared" si="7"/>
         <v>380</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F89" s="2">
+        <v>43</v>
+      </c>
+      <c r="G89" s="2">
+        <v>43</v>
+      </c>
+      <c r="H89" s="2">
+        <v>43</v>
+      </c>
+      <c r="I89" s="2">
+        <v>43</v>
+      </c>
+      <c r="J89" s="2">
+        <v>43</v>
+      </c>
+      <c r="K89" s="2">
+        <v>43</v>
+      </c>
+      <c r="L89" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="M89" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="N89" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="O89" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="P89" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>87</v>
       </c>
@@ -2263,8 +5557,44 @@
         <f t="shared" si="7"/>
         <v>385</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="G90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="H90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="I90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="J90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="K90" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="L90" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="M90" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="N90" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="O90" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="P90" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>88</v>
       </c>
@@ -2284,8 +5614,44 @@
         <f t="shared" si="7"/>
         <v>390</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F91" s="2">
+        <v>44</v>
+      </c>
+      <c r="G91" s="2">
+        <v>44</v>
+      </c>
+      <c r="H91" s="2">
+        <v>44</v>
+      </c>
+      <c r="I91" s="2">
+        <v>44</v>
+      </c>
+      <c r="J91" s="2">
+        <v>44</v>
+      </c>
+      <c r="K91" s="2">
+        <v>44</v>
+      </c>
+      <c r="L91" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="M91" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="N91" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="O91" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="P91" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>89</v>
       </c>
@@ -2305,8 +5671,44 @@
         <f t="shared" si="7"/>
         <v>395</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="G92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="H92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="I92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="J92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="K92" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="L92" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="M92" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="N92" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="O92" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="P92" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>90</v>
       </c>
@@ -2326,8 +5728,44 @@
         <f t="shared" si="7"/>
         <v>400</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F93" s="2">
+        <v>45</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45</v>
+      </c>
+      <c r="H93" s="2">
+        <v>45</v>
+      </c>
+      <c r="I93" s="2">
+        <v>45</v>
+      </c>
+      <c r="J93" s="2">
+        <v>45</v>
+      </c>
+      <c r="K93" s="2">
+        <v>45</v>
+      </c>
+      <c r="L93" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="M93" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="N93" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="O93" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="P93" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>91</v>
       </c>
@@ -2347,8 +5785,44 @@
         <f t="shared" si="7"/>
         <v>405</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="H94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="I94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="J94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="K94" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="L94" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="M94" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="N94" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="O94" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="P94" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>92</v>
       </c>
@@ -2368,8 +5842,44 @@
         <f t="shared" si="7"/>
         <v>410</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F95" s="2">
+        <v>46</v>
+      </c>
+      <c r="G95" s="2">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2">
+        <v>46</v>
+      </c>
+      <c r="I95" s="2">
+        <v>46</v>
+      </c>
+      <c r="J95" s="2">
+        <v>46</v>
+      </c>
+      <c r="K95" s="2">
+        <v>46</v>
+      </c>
+      <c r="L95" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="M95" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="N95" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="O95" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="P95" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="Q95" s="2">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>93</v>
       </c>
@@ -2389,8 +5899,44 @@
         <f t="shared" si="7"/>
         <v>415</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="G96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="H96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="I96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="J96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="K96" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="L96" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="M96" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="N96" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="O96" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="P96" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="Q96" s="2">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>94</v>
       </c>
@@ -2410,8 +5956,44 @@
         <f t="shared" si="7"/>
         <v>420</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F97" s="2">
+        <v>47</v>
+      </c>
+      <c r="G97" s="2">
+        <v>47</v>
+      </c>
+      <c r="H97" s="2">
+        <v>47</v>
+      </c>
+      <c r="I97" s="2">
+        <v>47</v>
+      </c>
+      <c r="J97" s="2">
+        <v>47</v>
+      </c>
+      <c r="K97" s="2">
+        <v>47</v>
+      </c>
+      <c r="L97" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="M97" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="N97" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="O97" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="P97" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="Q97" s="2">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>95</v>
       </c>
@@ -2431,8 +6013,44 @@
         <f t="shared" si="7"/>
         <v>425</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="G98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="H98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="I98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="J98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="K98" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="L98" s="2">
+        <v>27</v>
+      </c>
+      <c r="M98" s="2">
+        <v>27</v>
+      </c>
+      <c r="N98" s="2">
+        <v>27</v>
+      </c>
+      <c r="O98" s="2">
+        <v>27</v>
+      </c>
+      <c r="P98" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q98" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>96</v>
       </c>
@@ -2452,8 +6070,44 @@
         <f t="shared" si="7"/>
         <v>430</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F99" s="2">
+        <v>48</v>
+      </c>
+      <c r="G99" s="2">
+        <v>48</v>
+      </c>
+      <c r="H99" s="2">
+        <v>48</v>
+      </c>
+      <c r="I99" s="2">
+        <v>48</v>
+      </c>
+      <c r="J99" s="2">
+        <v>48</v>
+      </c>
+      <c r="K99" s="2">
+        <v>48</v>
+      </c>
+      <c r="L99" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="M99" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="N99" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="O99" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="P99" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="Q99" s="2">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>97</v>
       </c>
@@ -2473,8 +6127,44 @@
         <f t="shared" si="7"/>
         <v>435</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="G100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="H100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="I100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="J100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="K100" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="L100" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="M100" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="N100" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="O100" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="P100" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="Q100" s="2">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>98</v>
       </c>
@@ -2494,8 +6184,44 @@
         <f t="shared" si="7"/>
         <v>440</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101" s="2">
+        <v>49</v>
+      </c>
+      <c r="G101" s="2">
+        <v>49</v>
+      </c>
+      <c r="H101" s="2">
+        <v>49</v>
+      </c>
+      <c r="I101" s="2">
+        <v>49</v>
+      </c>
+      <c r="J101" s="2">
+        <v>49</v>
+      </c>
+      <c r="K101" s="2">
+        <v>49</v>
+      </c>
+      <c r="L101" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="M101" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="N101" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="O101" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="P101" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="Q101" s="2">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>99</v>
       </c>
@@ -2515,8 +6241,44 @@
         <f t="shared" si="7"/>
         <v>445</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="G102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="H102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="I102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="J102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="K102" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="L102" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="M102" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="N102" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="O102" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="P102" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="Q102" s="2">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>100</v>
       </c>
@@ -2535,6 +6297,42 @@
       <c r="E103" s="2">
         <f t="shared" si="7"/>
         <v>450</v>
+      </c>
+      <c r="F103" s="2">
+        <v>50</v>
+      </c>
+      <c r="G103" s="2">
+        <v>50</v>
+      </c>
+      <c r="H103" s="2">
+        <v>50</v>
+      </c>
+      <c r="I103" s="2">
+        <v>50</v>
+      </c>
+      <c r="J103" s="2">
+        <v>50</v>
+      </c>
+      <c r="K103" s="2">
+        <v>50</v>
+      </c>
+      <c r="L103" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="M103" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="N103" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="O103" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="P103" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="Q103" s="2">
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>
